--- a/data/sample_summary/2026/1-4月/1-4月客户类型样本统计表.xlsx
+++ b/data/sample_summary/2026/1-4月/1-4月客户类型样本统计表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangqijin/PycharmProjects/hangbo/data/sample_summary/2026/1-4月/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54B1E9A-CE3E-B14E-9B5F-012AA6808CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F211840F-4407-D74C-BAD6-788300FB17D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="23040" windowHeight="23680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,6 +160,7 @@
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="楷体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -167,6 +168,7 @@
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="楷体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -174,12 +176,14 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="楷体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="15"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -590,11 +594,7 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" customWidth="1"/>
+    <col min="1" max="8" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1">
